--- a/0-course-info/schedule_f26.xlsx
+++ b/0-course-info/schedule_f26.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/0-course-info/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C726383F-547B-8444-95A1-87A884512239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F50E0F2F-0771-984C-BC05-686B9958A6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{44A96070-E6A5-4735-BA92-AD6DC359C4CB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="131">
   <si>
     <t>Day</t>
   </si>
@@ -434,9 +434,6 @@
     <t xml:space="preserve">Note: Dr. C traveling this weekend </t>
   </si>
   <si>
-    <t>Activity 9.1 + Start Lab 4</t>
-  </si>
-  <si>
     <t>Lab 4 due 11/20</t>
   </si>
   <si>
@@ -447,15 +444,6 @@
   </si>
   <si>
     <t>Project Letter of Learning due Wed 12/16</t>
-  </si>
-  <si>
-    <t>Project Proposal due Wed 11/4</t>
-  </si>
-  <si>
-    <t>Mod 11: Survey Sampling</t>
-  </si>
-  <si>
-    <t>Mod 10: Writing Survey Instruments</t>
   </si>
   <si>
     <t>Discord and R / Rstudio Setup
@@ -466,6 +454,21 @@
   </si>
   <si>
     <t>Lab 1 due 9/8</t>
+  </si>
+  <si>
+    <t>Mod 10: Survey Sampling</t>
+  </si>
+  <si>
+    <t>Mod 11: Writing Survey Instruments</t>
+  </si>
+  <si>
+    <t>Final Project Proposal due Wed 11/4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Activity 9.1 + </t>
+  </si>
+  <si>
+    <t>Start Lab 4</t>
   </si>
 </sst>
 </file>
@@ -823,6 +826,15 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -835,19 +847,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1231,7 +1234,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="61">
+      <c r="A2" s="57">
         <v>1</v>
       </c>
       <c r="B2" s="3">
@@ -1254,7 +1257,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="61"/>
+      <c r="A3" s="57"/>
       <c r="B3" s="3">
         <v>2</v>
       </c>
@@ -1269,14 +1272,14 @@
         <v>72</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="62"/>
+      <c r="A4" s="58"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="17"/>
@@ -1284,11 +1287,11 @@
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="12" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A5" s="65">
+      <c r="A5" s="59">
         <v>2</v>
       </c>
       <c r="B5" s="2">
@@ -1314,7 +1317,7 @@
       <c r="H5" s="13"/>
     </row>
     <row r="6" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A6" s="61"/>
+      <c r="A6" s="57"/>
       <c r="B6" s="3">
         <f>B5+1</f>
         <v>4</v>
@@ -1337,7 +1340,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="62"/>
+      <c r="A7" s="58"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="17"/>
@@ -1347,7 +1350,7 @@
       <c r="H7" s="12"/>
     </row>
     <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="61">
+      <c r="A8" s="57">
         <v>3</v>
       </c>
       <c r="B8" s="3">
@@ -1371,11 +1374,11 @@
         <v>98</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="61"/>
+      <c r="A9" s="57"/>
       <c r="B9" s="3">
         <f>B8+1</f>
         <v>6</v>
@@ -1398,7 +1401,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="62"/>
+      <c r="A10" s="58"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="17"/>
@@ -1408,7 +1411,7 @@
       <c r="H10" s="12"/>
     </row>
     <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A11" s="65">
+      <c r="A11" s="59">
         <v>4</v>
       </c>
       <c r="B11" s="2">
@@ -1433,7 +1436,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="61"/>
+      <c r="A12" s="57"/>
       <c r="B12" s="29">
         <f>B11+1</f>
         <v>8</v>
@@ -1448,14 +1451,14 @@
       <c r="E12" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="F12" s="58" t="s">
+      <c r="F12" s="61" t="s">
         <v>117</v>
       </c>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
     </row>
     <row r="13" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="62"/>
+      <c r="A13" s="58"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="17"/>
@@ -1465,7 +1468,7 @@
       <c r="H13" s="14"/>
     </row>
     <row r="14" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="65">
+      <c r="A14" s="59">
         <v>5</v>
       </c>
       <c r="B14" s="2">
@@ -1491,7 +1494,7 @@
       <c r="H14" s="13"/>
     </row>
     <row r="15" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A15" s="61"/>
+      <c r="A15" s="57"/>
       <c r="B15" s="3">
         <f>B14+1</f>
         <v>10</v>
@@ -1515,7 +1518,7 @@
       <c r="H15" s="14"/>
     </row>
     <row r="16" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="62"/>
+      <c r="A16" s="58"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="17"/>
@@ -1527,7 +1530,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="65">
+      <c r="A17" s="59">
         <v>6</v>
       </c>
       <c r="B17" s="2">
@@ -1552,7 +1555,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="32" x14ac:dyDescent="0.2">
-      <c r="A18" s="61"/>
+      <c r="A18" s="57"/>
       <c r="B18" s="3">
         <f>B17+1</f>
         <v>12</v>
@@ -1575,7 +1578,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="62"/>
+      <c r="A19" s="58"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="17"/>
@@ -1584,7 +1587,7 @@
       <c r="H19" s="20"/>
     </row>
     <row r="20" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="65">
+      <c r="A20" s="59">
         <v>7</v>
       </c>
       <c r="B20" s="2">
@@ -1610,7 +1613,7 @@
       <c r="H20" s="8"/>
     </row>
     <row r="21" spans="1:9" ht="48" x14ac:dyDescent="0.2">
-      <c r="A21" s="61"/>
+      <c r="A21" s="57"/>
       <c r="B21" s="3">
         <f>B20+1</f>
         <v>14</v>
@@ -1633,18 +1636,18 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="62"/>
+      <c r="A22" s="58"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="17"/>
-      <c r="F22" s="57" t="s">
+      <c r="F22" s="60" t="s">
         <v>118</v>
       </c>
-      <c r="G22" s="57"/>
-      <c r="H22" s="57"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
     </row>
     <row r="23" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="65">
+      <c r="A23" s="59">
         <v>8</v>
       </c>
       <c r="B23" s="2">
@@ -1667,7 +1670,7 @@
       <c r="I23" s="11"/>
     </row>
     <row r="24" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="61"/>
+      <c r="A24" s="57"/>
       <c r="B24" s="3">
         <f>B23+1</f>
         <v>16</v>
@@ -1685,7 +1688,7 @@
       <c r="H24" s="23"/>
     </row>
     <row r="25" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="62"/>
+      <c r="A25" s="58"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="17"/>
@@ -1696,7 +1699,7 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="65">
+      <c r="A26" s="59">
         <v>9</v>
       </c>
       <c r="B26" s="53">
@@ -1718,7 +1721,7 @@
       <c r="H26" s="56"/>
     </row>
     <row r="27" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="61"/>
+      <c r="A27" s="57"/>
       <c r="B27" s="3">
         <f>B26+1</f>
         <v>18</v>
@@ -1734,12 +1737,12 @@
         <v>81</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="H27" s="22"/>
     </row>
     <row r="28" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="62"/>
+      <c r="A28" s="58"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="17"/>
@@ -1749,7 +1752,7 @@
       <c r="H28" s="12"/>
     </row>
     <row r="29" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="61">
+      <c r="A29" s="57">
         <v>10</v>
       </c>
       <c r="B29" s="2">
@@ -1766,10 +1769,13 @@
       <c r="E29" s="46" t="s">
         <v>81</v>
       </c>
+      <c r="G29" s="9" t="s">
+        <v>130</v>
+      </c>
       <c r="H29" s="9"/>
     </row>
     <row r="30" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="61"/>
+      <c r="A30" s="57"/>
       <c r="B30" s="3">
         <f>B29+1</f>
         <v>20</v>
@@ -1786,7 +1792,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="62"/>
+      <c r="A31" s="58"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="17"/>
@@ -1796,7 +1802,7 @@
       <c r="H31" s="15"/>
     </row>
     <row r="32" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="61">
+      <c r="A32" s="57">
         <v>11</v>
       </c>
       <c r="B32" s="2">
@@ -1814,11 +1820,11 @@
         <v>126</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="61"/>
+      <c r="A33" s="57"/>
       <c r="B33" s="3">
         <f>B32+1</f>
         <v>22</v>
@@ -1835,7 +1841,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="62"/>
+      <c r="A34" s="58"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="17"/>
@@ -1845,7 +1851,7 @@
       <c r="H34" s="15"/>
     </row>
     <row r="35" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A35" s="61">
+      <c r="A35" s="57">
         <v>12</v>
       </c>
       <c r="B35" s="2">
@@ -1860,12 +1866,12 @@
         <v>46336</v>
       </c>
       <c r="E35" s="46" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="H35" s="9"/>
     </row>
     <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A36" s="61"/>
+      <c r="A36" s="57"/>
       <c r="B36" s="3">
         <f>B35+1</f>
         <v>24</v>
@@ -1878,11 +1884,11 @@
         <v>46338</v>
       </c>
       <c r="E36" s="46" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="62"/>
+      <c r="A37" s="58"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="D37" s="17"/>
@@ -1892,7 +1898,7 @@
       <c r="H37" s="15"/>
     </row>
     <row r="38" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A38" s="61">
+      <c r="A38" s="57">
         <v>13</v>
       </c>
       <c r="B38" s="2">
@@ -1907,12 +1913,12 @@
         <v>46343</v>
       </c>
       <c r="E38" s="46" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H38" s="9"/>
     </row>
     <row r="39" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="61"/>
+      <c r="A39" s="57"/>
       <c r="B39" s="3">
         <f>B38+1</f>
         <v>26</v>
@@ -1925,11 +1931,12 @@
         <v>46345</v>
       </c>
       <c r="E39" s="46" t="s">
-        <v>83</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="F39" s="46"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="62"/>
+      <c r="A40" s="58"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="17"/>
@@ -1937,11 +1944,11 @@
       <c r="F40" s="19"/>
       <c r="G40" s="19"/>
       <c r="H40" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="63"/>
+      <c r="A41" s="64"/>
       <c r="B41" s="32"/>
       <c r="C41" s="31" t="s">
         <v>3</v>
@@ -1956,7 +1963,7 @@
       <c r="H41" s="34"/>
     </row>
     <row r="42" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A42" s="63"/>
+      <c r="A42" s="64"/>
       <c r="B42" s="31"/>
       <c r="C42" s="31" t="s">
         <v>12</v>
@@ -1973,7 +1980,7 @@
       <c r="H42" s="36"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="64"/>
+      <c r="A43" s="65"/>
       <c r="B43" s="37"/>
       <c r="C43" s="37"/>
       <c r="D43" s="38"/>
@@ -1983,7 +1990,7 @@
       <c r="H43" s="40"/>
     </row>
     <row r="44" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="61">
+      <c r="A44" s="57">
         <v>14</v>
       </c>
       <c r="B44" s="2">
@@ -2003,7 +2010,7 @@
       <c r="H44" s="9"/>
     </row>
     <row r="45" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A45" s="61"/>
+      <c r="A45" s="57"/>
       <c r="B45" s="3">
         <f>B44+1</f>
         <v>28</v>
@@ -2020,7 +2027,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="62"/>
+      <c r="A46" s="58"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="17">
@@ -2033,7 +2040,7 @@
       <c r="H46" s="15"/>
     </row>
     <row r="47" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A47" s="61">
+      <c r="A47" s="57">
         <v>15</v>
       </c>
       <c r="B47" s="2">
@@ -2051,11 +2058,11 @@
         <v>84</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="61"/>
+      <c r="A48" s="57"/>
       <c r="B48" s="3">
         <f>B47+1</f>
         <v>30</v>
@@ -2071,11 +2078,11 @@
         <v>82</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="62"/>
+      <c r="A49" s="58"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
       <c r="D49" s="17">
@@ -2088,7 +2095,7 @@
       <c r="H49" s="15"/>
     </row>
     <row r="50" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A50" s="61"/>
+      <c r="A50" s="57"/>
       <c r="B50" s="2"/>
       <c r="C50" s="3" t="s">
         <v>3</v>
@@ -2100,12 +2107,12 @@
       <c r="E50" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="H50" s="59" t="s">
-        <v>123</v>
+      <c r="H50" s="62" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A51" s="61"/>
+      <c r="A51" s="57"/>
       <c r="C51" s="3" t="s">
         <v>12</v>
       </c>
@@ -2116,10 +2123,10 @@
       <c r="E51" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="H51" s="60"/>
+      <c r="H51" s="63"/>
     </row>
     <row r="52" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A52" s="62"/>
+      <c r="A52" s="58"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="17"/>
@@ -2132,6 +2139,15 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="H50:H51"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A47:A49"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A8:A10"/>
@@ -2143,15 +2159,6 @@
     <mergeCell ref="A26:A28"/>
     <mergeCell ref="A29:A31"/>
     <mergeCell ref="A17:A19"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="H50:H51"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A47:A49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="78" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
